--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260804.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260804.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>3.83%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.84%</t>
+          <t>3.80%</t>
         </is>
       </c>
     </row>
@@ -660,24 +660,24 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.42%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>46,121,000</t>
+          <t>5,972,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -689,22 +689,22 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>5,972,000</t>
+          <t>46,121,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.18%</t>
         </is>
       </c>
     </row>
@@ -726,161 +726,161 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>21,105,000</t>
+          <t>9,790,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>9,790,000</t>
+          <t>19,587,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>19,587,000</t>
+          <t>21,105,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>25,898,000</t>
+          <t>3,801,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.63%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>34,365,000</t>
+          <t>30,079,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.60%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>3,801,000</t>
+          <t>25,898,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.60%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>30,079,000</t>
+          <t>34,365,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
@@ -946,95 +946,95 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2,820,000</t>
+          <t>9,520,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>9,520,000</t>
+          <t>2,820,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>33,782,000</t>
+          <t>20,683,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>20,683,000</t>
+          <t>33,782,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,815,579,584</t>
+          <t>2,929,621,425</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.16%</t>
         </is>
       </c>
     </row>
@@ -1100,95 +1100,95 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>8,904,000</t>
+          <t>15,056,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>17,369,000</t>
+          <t>40,734,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>40,734,000</t>
+          <t>17,369,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>15,056,000</t>
+          <t>8,904,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
@@ -1249,78 +1249,78 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,323,465,322</t>
+          <t>2,338,465,322</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>5,975,000</t>
+          <t>518,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>13,785,000</t>
+          <t>5,975,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>518,000</t>
+          <t>13,785,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
@@ -1408,51 +1408,51 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>至上電子</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>23,205,000</t>
+          <t>22,613,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>至上電子</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>22,613,000</t>
+          <t>23,205,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
@@ -1474,51 +1474,51 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>8,951,000</t>
+          <t>7,223,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>7,223,000</t>
+          <t>8,951,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
@@ -1562,117 +1562,117 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>47,231,000</t>
+          <t>18,691,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>18,691,000</t>
+          <t>47,231,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>48,929,000</t>
+          <t>2,088,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,088,000</t>
+          <t>6,330,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>6,330,000</t>
+          <t>48,929,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11,181,870</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
     </row>
